--- a/frontend/public/ejemplos/pce_simplificada_niif9/RQ-003_castigos.xlsx
+++ b/frontend/public/ejemplos/pce_simplificada_niif9/RQ-003_castigos.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,18 +437,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F-11</t>
+          <t>001-001-000001008</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+          <t>Minera Austral S.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2401.38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>001-001-000001010</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hidrosur Cía. Ltda.</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1243.47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>001-001-000001014</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Minera Austral S.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2386.85</v>
       </c>
     </row>
   </sheetData>
